--- a/sample_output.xlsx
+++ b/sample_output.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Graphite Heather / Wax ---</t>
+          <t>Graphite Heather / Wax</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Cold Blue Heather / Wax ---</t>
+          <t>Cold Blue Heather / Wax</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Light Clay Heather / Wax ---</t>
+          <t>Light Clay Heather / Wax</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Graphite Heather / Wax ---</t>
+          <t>Graphite Heather / Wax</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Cold Blue Heather / Wax ---</t>
+          <t>Cold Blue Heather / Wax</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Light Clay Heather / Wax ---</t>
+          <t>Light Clay Heather / Wax</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Graphite Heather ---</t>
+          <t>Graphite Heather</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Cozy Blue Heather ---</t>
+          <t>Cozy Blue Heather</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Dilworth Stripe, Blue ---</t>
+          <t>Dilworth Stripe, Blue</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Dilworth Stripe, Wip H Brown ---</t>
+          <t>Dilworth Stripe, Wip H Brown</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Dilworth Stripe, Graphite ---</t>
+          <t>Dilworth Stripe, Graphite</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Logue Stripe, Blue Heather ---</t>
+          <t>Logue Stripe, Blue Heather</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Logue Stripe, Graphite Heather ---</t>
+          <t>Logue Stripe, Graphite Heather</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Logue Stripe, WIP H Brown Heather ---</t>
+          <t>Logue Stripe, WIP H Brown Heather</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>White ---</t>
+          <t>White</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Cozy Blue ---</t>
+          <t>Cozy Blue</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Black ---</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>White ---</t>
+          <t>White</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Cold Blue ---</t>
+          <t>Cold Blue</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Black ---</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>White ---</t>
+          <t>White</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Black ---</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>White ---</t>
+          <t>White</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Black ---</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Blue ---</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>White ---</t>
+          <t>White</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Black ---</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
